--- a/feedback_surveys/002_marina_scheduling_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/002_marina_scheduling_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{1:_'boat_ramp'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{1: 'Boat Ramp'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{2:_'restrooms'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{2: 'Restrooms'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{3:_'parking'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{3: 'Parking'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{4:_'restaurant'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{4: 'Restaurant'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{5:_'marina_office'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{5: 'Marina Office'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{6:_'information_center'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{6: 'Information Center'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{7:_'boat_wash_station'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{7: 'Boat Wash Station'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{1:_'wi-fi'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{1: 'Wi-Fi'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{2:_'free_parking'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{2: 'Free Parking'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{3:_'free_restrooms'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{3: 'Free Restrooms'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{4:_'boat_trailer_parking'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{4: 'Boat Trailer Parking'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{5:_'marina_office'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{5: 'Marina Office'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{1:_'safety_briefing'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{1: 'Safety Briefing'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{2:_'hazard_signage'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{2: 'Hazard Signage'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{3:_'marina_emergency_contact'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{3: 'Marina Emergency Contact'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{4:_'first_aid_kit'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{4: 'First Aid Kit'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{5:_'emergency_phone'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{5: 'Emergency Phone'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
